--- a/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de papa. Jeanne dessine un soleil. Maman aide. Maman dit : c'est une surprise gentille. On la garde un peu. Jeanne cache le dessin. Le papier est dans le tiroir. Papa passe. Jeanne sourit. Elle garde un peu. Puis on dit. Maman dit : maintenant, on révèle. Jeanne ouvre le tiroir. Elle tend le dessin. Jeanne dit : c'est pour toi, papa. Papa rit. Il colle le soleil. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Jeanne tape des mains. Le dessin est jaune. Papa dit merci.</t>
+          <t>C'est bientôt l'anniversaire de papa. Jeanne dessine un soleil. Maman aide. C'est une surprise gentille. On la garde un peu. Jeanne cache le dessin. Le papier est dans le tiroir. Papa passe. Jeanne sourit. Elle garde un peu. Puis on dit. Maintenant, on révèle. Jeanne ouvre le tiroir. Elle tend le dessin. C'est pour toi, papa. Papa rit. Il colle le soleil. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Jeanne tape des mains. Le dessin est jaune. Papa dit merci.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est bientôt l'anniversaire de papa. Jeanne dessine un soleil. Maman aide.
+maman|C'est une surprise gentille. On la garde un peu.
+narrateur|Jeanne cache le dessin. Le papier est dans le tiroir. Papa passe. Jeanne sourit. Elle garde un peu. Puis on dit.
+maman|Maintenant, on révèle.
+narrateur|Jeanne ouvre le tiroir. Elle tend le dessin.
+enfant-f|C'est pour toi, papa. Papa rit. Il colle le soleil. C'était une surprise gentille. On l'a gardée un peu.
+narrateur|Puis on dit. Jeanne tape des mains. Le dessin est jaune. Papa dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Jeanne cache un dessin. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jeanne a gardé un peu. Puis on dit. C'était une surprise gentille pour papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa accroche le soleil. Jeanne boit un verre d'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Puis on dit. Jeanne tape des mains. Le dessin est jaune. Papa dit merci.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Jeanne cache un dessin. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Jeanne a gardé un peu. Puis on dit. C'était une surprise gentille pour papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Papa accroche le soleil. Jeanne boit un verre d'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La surprise gentille de Jeanne</t>
+          <t>Le soleil de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina dessine un soleil. Elle le cache dans le tiroir. Elle garde un peu. Puis elle dit. Papa accroche le dessin.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de papa. Jeanne dessine un soleil. Maman aide. C'est une surprise gentille. On la garde un peu. Jeanne cache le dessin. Le papier est dans le tiroir. Papa passe. Jeanne sourit. Elle garde un peu. Puis on dit. Maintenant, on révèle. Jeanne ouvre le tiroir. Elle tend le dessin. C'est pour toi, papa. Papa rit. Il colle le soleil. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Jeanne tape des mains. Le dessin est jaune. Papa dit merci.</t>
+          <t>La nappe à carreaux est un peu froissée. Un crayon jaune attend sur le bord. La maison sent le papier. Dehors, un oiseau chante tout bas. La lumière est douce, jaune. Les chaises sont un peu froides. Un verre d'eau laisse un rond. Le rond brille sur le bois. Papa range des chaussures, plus loin. On entend un bruit de semelle. Maman est près de Nina. Tu entends l'oiseau ? Oui. Il chante. Tu veux dessiner, Nina ? Un soleil, maman. Le jaune est tout chaud. Bientôt, c'est l'anniversaire de papa. En ce moment, Nina dessine un soleil. Le papier est blanc, lisse. Le soleil a un grand rond. Il a des rayons courts. Un rayon ici. Et un ici. Le crayon fait un bruit sec. Il est tout jaune. Comme le vrai soleil. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nina cache le dessin. Le tiroir sent le bois. Le papier glisse dedans. On ferme tout doux. Papa passe près de la table. Ça sent les crayons ici. Je ne dis rien encore. Encore un tout petit peu. Nina serre les lèvres. Elle garde encore un peu. Je vais chercher un verre. Maintenant, on dit. Nina ouvre le tiroir. Elle tend le soleil. C'est pour toi, papa. Surprise. Un soleil. Merci, Nina. Une surprise gentille. On la garde un peu. Puis on dit. Puis on dit. Je le colle ici. Le soleil est jaune, tout rond. Bravo, Nina. Tu as fait du bon travail. Il est pour toi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est bientôt l'anniversaire de papa. Jeanne dessine un soleil. Maman aide.
-maman|C'est une surprise gentille. On la garde un peu.
-narrateur|Jeanne cache le dessin. Le papier est dans le tiroir. Papa passe. Jeanne sourit. Elle garde un peu. Puis on dit.
-maman|Maintenant, on révèle.
-narrateur|Jeanne ouvre le tiroir. Elle tend le dessin.
-enfant-f|C'est pour toi, papa. Papa rit. Il colle le soleil. C'était une surprise gentille. On l'a gardée un peu.
-narrateur|Puis on dit. Jeanne tape des mains. Le dessin est jaune. Papa dit merci.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La nappe à carreaux est un peu froissée.
+narrateur|Un crayon jaune attend sur le bord.
+narrateur|La maison sent le papier.
+narrateur|Dehors, un oiseau chante tout bas.
+narrateur|La lumière est douce, jaune.
+narrateur|Les chaises sont un peu froides.
+narrateur|Un verre d'eau laisse un rond.
+narrateur|Le rond brille sur le bois.
+narrateur|Papa range des chaussures, plus loin.
+narrateur|On entend un bruit de semelle.
+narrateur|Maman est près de Nina.
+maman|Tu entends l'oiseau ?
+enfant-f|Oui. Il chante.
+maman|Tu veux dessiner, Nina ?
+enfant-f|Un soleil, maman.
+maman|Le jaune est tout chaud.
+narrateur|Bientôt, c'est l'anniversaire de papa.
+narrateur|En ce moment, Nina dessine un soleil.
+narrateur|Le papier est blanc, lisse.
+narrateur|Le soleil a un grand rond.
+narrateur|Il a des rayons courts.
+maman|Un rayon ici.
+enfant-f|Et un ici.
+narrateur|Le crayon fait un bruit sec.
+maman|Il est tout jaune.
+enfant-f|Comme le vrai soleil.
+maman|C'est une surprise gentille.
+maman|On la garde un peu.
+enfant-f|On la garde un peu.
+narrateur|Nina cache le dessin.
+narrateur|Le tiroir sent le bois.
+narrateur|Le papier glisse dedans.
+maman|On ferme tout doux.
+narrateur|Papa passe près de la table.
+papa|Ça sent les crayons ici.
+enfant-f|Je ne dis rien encore.
+maman|Encore un tout petit peu.
+narrateur|Nina serre les lèvres.
+narrateur|Elle garde encore un peu.
+papa|Je vais chercher un verre.
+maman|Maintenant, on dit.
+narrateur|Nina ouvre le tiroir.
+narrateur|Elle tend le soleil.
+enfant-f|C'est pour toi, papa.
+enfant-f|Surprise.
+papa|Un soleil.
+papa|Merci, Nina.
+maman|Une surprise gentille.
+maman|On la garde un peu.
+maman|Puis on dit.
+enfant-f|Puis on dit.
+papa|Je le colle ici.
+narrateur|Le soleil est jaune, tout rond.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+enfant-f|Il est pour toi.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>tiroir</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jeanne cache un dessin. C'est quoi ?</t>
+          <t>Nina cache un dessin. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Jeanne cache un dessin. C'est quoi ?</t>
+          <t>narrateur|Nina cache un dessin.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jeanne a gardé un peu. Puis on dit. C'était une surprise gentille pour papa.</t>
+          <t>Nina a gardé un peu. Puis on dit. C'était une surprise gentille. Pour moi. Surprise gentille. Puis on dit. Bravo, Nina. Le crayon jaune repose. Tu as gardé, puis tu as dit. Oui, papa. Le tiroir est refermé. Le soleil est sorti. Il est à sa place.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1740,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jeanne a gardé un peu. Puis on dit. C'était une surprise gentille pour papa.</t>
+          <t>narrateur|Nina a gardé un peu.
+narrateur|Puis on dit.
+maman|C'était une surprise gentille.
+papa|Pour moi.
+enfant-f|Surprise gentille.
+enfant-f|Puis on dit.
+maman|Bravo, Nina.
+narrateur|Le crayon jaune repose.
+papa|Tu as gardé, puis tu as dit.
+enfant-f|Oui, papa.
+maman|Le tiroir est refermé.
+enfant-f|Le soleil est sorti.
+papa|Il est à sa place.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa accroche le soleil. Jeanne boit un verre d'eau.</t>
+          <t>Papa accroche le soleil. Le papier est un peu chaud. Il est jaune. Oui, tout jaune. Tu as gardé un peu. Puis tu as dit. Nina boit un verre d'eau. L'eau est fraîche. Merci encore. De rien, papa. L'oiseau chante encore, dehors. On range le crayon. Dans la boîte. Bravo. La nappe est encore froissée. On boit un peu d'eau. Elle est fraîche. Le soleil est à sa place. Le rond du verre sèche.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1916,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa accroche le soleil. Jeanne boit un verre d'eau.</t>
+          <t>narrateur|Papa accroche le soleil.
+narrateur|Le papier est un peu chaud.
+enfant-f|Il est jaune.
+papa|Oui, tout jaune.
+maman|Tu as gardé un peu.
+maman|Puis tu as dit.
+narrateur|Nina boit un verre d'eau.
+narrateur|L'eau est fraîche.
+papa|Merci encore.
+enfant-f|De rien, papa.
+narrateur|L'oiseau chante encore, dehors.
+maman|On range le crayon.
+enfant-f|Dans la boîte.
+papa|Bravo.
+narrateur|La nappe est encore froissée.
+maman|On boit un peu d'eau.
+enfant-f|Elle est fraîche.
+papa|Le soleil est à sa place.
+narrateur|Le rond du verre sèche.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Nina. Le soleil est là. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2102,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a gardé un peu.
+enfant-f|Puis on a dit.
+maman|Bravo, Nina.
+papa|Le soleil est là.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2166,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La nappe à carreaux est un peu froissée. Un crayon jaune attend sur le bord. La maison sent le papier. Dehors, un oiseau chante tout bas. La lumière est douce, jaune. Les chaises sont un peu froides. Un verre d'eau laisse un rond. Le rond brille sur le bois. Papa range des chaussures, plus loin. On entend un bruit de semelle. Maman est près de Nina. Tu entends l'oiseau ? Oui. Il chante. Tu veux dessiner, Nina ? Un soleil, maman. Le jaune est tout chaud. Bientôt, c'est l'anniversaire de papa. En ce moment, Nina dessine un soleil. Le papier est blanc, lisse. Le soleil a un grand rond. Il a des rayons courts. Un rayon ici. Et un ici. Le crayon fait un bruit sec. Il est tout jaune. Comme le vrai soleil. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nina cache le dessin. Le tiroir sent le bois. Le papier glisse dedans. On ferme tout doux. Papa passe près de la table. Ça sent les crayons ici. Je ne dis rien encore. Encore un tout petit peu. Nina serre les lèvres. Elle garde encore un peu. Je vais chercher un verre. Maintenant, on dit. Nina ouvre le tiroir. Elle tend le soleil. C'est pour toi, papa. Surprise. Un soleil. Merci, Nina. Une surprise gentille. On la garde un peu. Puis on dit. Puis on dit. Je le colle ici. Le soleil est jaune, tout rond. Bravo, Nina. Tu as fait du bon travail. Il est pour toi.</t>
+          <t>La nappe à carreaux est un peu froissée. Un crayon jaune attend sur le bord. La maison sent le papier. Dehors, un oiseau chante tout bas. La lumière est douce, jaune. Les chaises sont un peu froides. Un verre d'eau laisse un rond. Le rond brille sur le bois. Papa range des chaussures, plus loin. On entend un bruit de semelle. Maman tient le crayon bleu. Tu entends l'oiseau ? Oui. Il chante. Tu veux dessiner, Nina ? Un soleil, maman. Le jaune est tout chaud. Bientôt, c'est l'anniversaire de papa. En ce moment, Nina dessine un soleil. Le papier est blanc, lisse. Le soleil a un grand rond. Il a des rayons courts. Un rayon ici. Et un ici. Le crayon fait un bruit sec. Il est tout jaune. Comme le vrai soleil. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nina cache le dessin. Le tiroir sent le bois. Le papier glisse dedans. On ferme tout doux. Papa passe près de la table. Ça sent les crayons ici. Je ne dis rien encore. Encore un tout petit peu. Nina serre les lèvres. Elle garde encore un peu. Je vais chercher un verre. Maintenant, on dit. Nina ouvre le tiroir. Elle tend le soleil. C'est pour toi, papa. Surprise. Un soleil. Merci, Nina. Une surprise gentille. On la garde un peu. Puis on dit. Puis on dit. Je le colle ici. Le soleil est jaune, tout rond. Bravo, Nina. Il est pour toi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est bientôt l'anniversaire de papa. Jeanne dessine un soleil. Maman aide. Maman dit : c'est une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille. On la garde un peu. Jeanne cache le dessin. Le papier est dans le tiroir. Papa passe. Jeanne sourit. Elle garde un peu. Puis on dit. Maman dit : maintenant, on révèle. Jeanne ouvre le tiroir. Elle tend le dessin. Jeanne dit : c'est pour toi, papa. Papa rit. Il colle le soleil. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Jeanne tape des mains. Le dessin est jaune. Papa dit merci.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La nappe à carreaux est un peu froissée. Un crayon jaune attend sur le bord. La maison sent le papier. Dehors, un oiseau chante tout bas. La lumière est douce, jaune. Les chaises sont un peu froides. Un verre d'eau laisse un rond. Le rond brille sur le bois. Papa range des chaussures, plus loin. On entend un bruit de semelle. Maman tient le crayon bleu. Tu entends l'oiseau ? Oui. Il chante. Tu veux dessiner, Nina ? Un soleil, maman. Le jaune est tout chaud. Bientôt, c'est l'anniversaire de papa. En ce moment, Nina dessine un soleil. Le papier est blanc, lisse. Le soleil a un grand rond. Il a des rayons courts. Un rayon ici. Et un ici. Le crayon fait un bruit sec. Il est tout jaune. Comme le vrai soleil. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nina cache le dessin. Le tiroir sent le bois. Le papier glisse dedans. On ferme tout doux. Papa passe près de la table. Ça sent les crayons ici. Je ne dis rien encore. Encore un tout petit peu. Nina serre les lèvres. Elle garde encore un peu. Je vais chercher un verre. Maintenant, on dit. Nina ouvre le tiroir. Elle tend le soleil. C'est pour toi, papa. Surprise. Un soleil. Merci, Nina. Une surprise gentille. On la garde un peu. Puis on dit. Puis on dit. Je le colle ici. Le soleil est jaune, tout rond. Bravo, Nina. Il est pour toi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1334,9 +1334,10 @@
 narrateur|Le rond brille sur le bois.
 narrateur|Papa range des chaussures, plus loin.
 narrateur|On entend un bruit de semelle.
-narrateur|Maman est près de Nina.
+narrateur|Maman tient le crayon bleu.
 maman|Tu entends l'oiseau ?
-enfant-f|Oui. Il chante.
+enfant-f|Oui.
+enfant-f|Il chante.
 maman|Tu veux dessiner, Nina ?
 enfant-f|Un soleil, maman.
 maman|Le jaune est tout chaud.
@@ -1378,7 +1379,6 @@
 papa|Je le colle ici.
 narrateur|Le soleil est jaune, tout rond.
 papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
 enfant-f|Il est pour toi.</t>
         </is>
       </c>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jeanne cache un dessin. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina cache un dessin. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1571,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,7 +1600,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jeanne a gardé un peu. Puis on dit. C'était une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille pour papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a gardé un peu. Puis on dit. C'était une surprise gentille. Pour moi. Surprise gentille. Puis on dit. Bravo, Nina. Le crayon jaune repose. Tu as gardé, puis tu as dit. Oui, papa. Le tiroir est refermé. Le soleil est sorti. Il est à sa place.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1755,7 +1754,6 @@
 papa|Il est à sa place.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa accroche le soleil. Jeanne boit un verre d'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa accroche le soleil. Le papier est un peu chaud. Il est jaune. Oui, tout jaune. Tu as gardé un peu. Puis tu as dit. Nina boit un verre d'eau. L'eau est fraîche. Merci encore. De rien, papa. L'oiseau chante encore, dehors. On range le crayon. Dans la boîte. Bravo. La nappe est encore froissée. On boit un peu d'eau. Elle est fraîche. Le soleil est à sa place. Le rond du verre sèche.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1935,6 @@
 narrateur|Le rond du verre sèche.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1962,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a gardé un peu. Puis on a dit. Bravo, Nina. Le soleil est là. L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Nina. Le soleil est là.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Nina. Le soleil est là.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,11 +2102,9 @@
           <t>enfant-f|On a gardé un peu.
 enfant-f|Puis on a dit.
 maman|Bravo, Nina.
-papa|Le soleil est là.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Le soleil est là.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2128,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2173,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine, table et tiroir</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jeanne, maman, papa</t>
+          <t>Nina, papa, maman</t>
         </is>
       </c>
     </row>
